--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484870_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484870_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3864</v>
+        <v>7.6577</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3056</v>
+        <v>6.3387</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0809</v>
+        <v>1.319</v>
       </c>
       <c r="G2" t="n">
         <v>6.5006</v>
@@ -610,13 +610,13 @@
         <v>1.5096</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.4954</v>
+        <v>-1.2242</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4574</v>
+        <v>-0.4242</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0381</v>
+        <v>-0.8</v>
       </c>
       <c r="V2" t="n">
         <v>1.0603</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4762</v>
+        <v>4.4783</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3565</v>
+        <v>3.2792</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1197</v>
+        <v>1.199</v>
       </c>
       <c r="G3" t="n">
         <v>3.9135</v>
@@ -688,13 +688,13 @@
         <v>1.6983</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1364</v>
+        <v>0.1384</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7265</v>
+        <v>0.6492</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5901</v>
+        <v>-0.5107</v>
       </c>
       <c r="V3" t="n">
         <v>0.8037</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5862</v>
+        <v>1.5137</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0321</v>
+        <v>0.7268</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5541</v>
+        <v>0.7869</v>
       </c>
       <c r="G4" t="n">
         <v>0.9272</v>
@@ -766,13 +766,13 @@
         <v>1.1322</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6101</v>
+        <v>0.5376</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9668</v>
+        <v>0.6615</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6433</v>
+        <v>-0.1239</v>
       </c>
       <c r="V4" t="n">
         <v>0.8037</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. VILAGRAN GONZALEZ</t>
+          <t>A. VALDERRAMA CARREÑO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9609</v>
+        <v>0.9339</v>
       </c>
       <c r="E5" t="n">
-        <v>0.645</v>
+        <v>0.9339</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3159</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3897</v>
+        <v>0.9339</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7795</v>
+        <v>0.317</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1692</v>
+        <v>0.617</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2426</v>
+        <v>0.9339</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0565</v>
+        <v>0.317</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2991</v>
+        <v>0.617</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1471</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.277</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1299</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4637</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0763</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3874</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA CARREÑO</t>
+          <t>A. VILAGRAN GONZALEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9339</v>
+        <v>0.3292</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9339</v>
+        <v>0.1192</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.2101</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9339</v>
+        <v>-0.3897</v>
       </c>
       <c r="H6" t="n">
-        <v>0.317</v>
+        <v>0.7795</v>
       </c>
       <c r="I6" t="n">
-        <v>0.617</v>
+        <v>-1.1692</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9339</v>
+        <v>-0.2426</v>
       </c>
       <c r="K6" t="n">
-        <v>0.317</v>
+        <v>1.0565</v>
       </c>
       <c r="L6" t="n">
-        <v>0.617</v>
+        <v>-1.2991</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.1471</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.277</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.1299</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.1887</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.3774</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.8321</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.5505</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.2816</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. MAS GANDIA</t>
+          <t>A. VALDERRAMA CARRENO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4152</v>
+        <v>-1.1475</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9003</v>
+        <v>-2.3569</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4852</v>
+        <v>1.2094</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4449</v>
+        <v>-1.2591</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4946</v>
+        <v>-0.5815</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0496</v>
+        <v>-0.6776</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5577</v>
+        <v>-0.9433</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0423</v>
+        <v>0.2324</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5999</v>
+        <v>-1.1757</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1127</v>
+        <v>-0.3158</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5369</v>
+        <v>-0.8139</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6496</v>
+        <v>0.4981</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3774</v>
+        <v>1.887</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4421</v>
+        <v>-0.0054</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3992</v>
+        <v>0.1715</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0429</v>
+        <v>-0.1769</v>
       </c>
       <c r="V8" t="n">
-        <v>0.038</v>
+        <v>-0.8265</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>0.038</v>
+        <v>-0.1849</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA CARRENO</t>
+          <t>R. MAS GANDIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4889</v>
+        <v>-1.2384</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5131</v>
+        <v>-1.8029</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0242</v>
+        <v>0.5645</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2591</v>
+        <v>-0.4449</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5815</v>
+        <v>-0.4946</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6776</v>
+        <v>0.0496</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9433</v>
+        <v>-0.5577</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2324</v>
+        <v>0.0423</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1757</v>
+        <v>-0.5999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3158</v>
+        <v>0.1127</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8139</v>
+        <v>-0.5369</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4981</v>
+        <v>0.6496</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9435</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R9" t="n">
-        <v>1.887</v>
+        <v>0.3774</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3468</v>
+        <v>-0.2653</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0152</v>
+        <v>-0.3017</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3621</v>
+        <v>0.0365</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8265</v>
+        <v>0.038</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1849</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8797</v>
+        <v>-1.7667</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0353</v>
+        <v>-2.6842</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1557</v>
+        <v>0.9176</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0714</v>
@@ -1234,13 +1234,13 @@
         <v>1.1322</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1352</v>
+        <v>0.2482</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.458</v>
+        <v>-0.1069</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.3551</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1058</v>
+        <v>-3.8064</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5164</v>
+        <v>-3.6138</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5895</v>
+        <v>-0.1927</v>
       </c>
       <c r="G11" t="n">
         <v>-3.0348</v>
@@ -1312,13 +1312,13 @@
         <v>0.9435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6637</v>
+        <v>-0.3643</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2787</v>
+        <v>-0.3761</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.385</v>
+        <v>0.0118</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1621</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. RAMOS CAMPOS</t>
+          <t>J. SANTONJA FERRERO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.109</v>
+        <v>-4.2374</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1857</v>
+        <v>-4.8398</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9233</v>
+        <v>0.6024</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.9383</v>
+        <v>-4.1652</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4439</v>
+        <v>-1.9737</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.3822</v>
+        <v>-2.1915</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.5083</v>
+        <v>-4.1346</v>
       </c>
       <c r="K12" t="n">
-        <v>2.372</v>
+        <v>-0.4273</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.8803</v>
+        <v>-3.7073</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.43</v>
+        <v>-0.0306</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9281</v>
+        <v>-1.5464</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4981</v>
+        <v>1.5158</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1322</v>
+        <v>1.5096</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7548</v>
+        <v>1.5096</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7842</v>
+        <v>-1.1213</v>
       </c>
       <c r="T12" t="n">
-        <v>0.606</v>
+        <v>-0.3654</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1782</v>
+        <v>-0.7559</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8226</v>
+        <v>-0.4605</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6036</v>
+        <v>-0.3398</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.4262</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. SANTONJA FERRERO</t>
+          <t>N. RAMOS CAMPOS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.535</v>
+        <v>-4.3185</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.8729</v>
+        <v>-2.263</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3379</v>
+        <v>-2.0556</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.1652</v>
+        <v>-1.9383</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.9737</v>
+        <v>1.4439</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.1915</v>
+        <v>-3.3822</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.1346</v>
+        <v>-1.5083</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4273</v>
+        <v>2.372</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.7073</v>
+        <v>-3.8803</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0306</v>
+        <v>-0.43</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5464</v>
+        <v>-0.9281</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5158</v>
+        <v>0.4981</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5096</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5096</v>
+        <v>0.7548</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.419</v>
+        <v>0.5746</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3986</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0204</v>
+        <v>0.0459</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.4605</v>
+        <v>-1.8226</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3398</v>
+        <v>0.6036</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1207</v>
+        <v>-2.4262</v>
       </c>
     </row>
     <row r="14">
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.872999999999999</v>
+        <v>-1.285100000000003</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.433599999999998</v>
+        <v>-5.845799999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>4.5608</v>
+        <v>4.5606</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2887999999999993</v>
+        <v>0.2888000000000011</v>
       </c>
       <c r="H14" t="n">
         <v>-3.4981</v>
@@ -1519,7 +1519,7 @@
         <v>3.7868</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5273999999999992</v>
+        <v>0.5273999999999994</v>
       </c>
       <c r="K14" t="n">
         <v>4.9693</v>
@@ -1528,16 +1528,16 @@
         <v>-4.4417</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2388</v>
+        <v>-0.2387999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.467499999999999</v>
+        <v>-8.467500000000001</v>
       </c>
       <c r="O14" t="n">
         <v>8.2287</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9434999999999999</v>
+        <v>0.9434999999999998</v>
       </c>
       <c r="Q14" t="n">
         <v>-10.3785</v>
@@ -1546,10 +1546,10 @@
         <v>11.322</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2374</v>
+        <v>-0.6496</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3988999999999998</v>
+        <v>0.9870999999999999</v>
       </c>
       <c r="U14" t="n">
         <v>-1.6365</v>
@@ -1561,7 +1561,7 @@
         <v>3.018</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.885800000000001</v>
+        <v>-4.8858</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.964</v>
+        <v>2.1549</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4771</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4869</v>
+        <v>1.4316</v>
       </c>
       <c r="G15" t="n">
         <v>-1.4606</v>
@@ -1624,13 +1624,13 @@
         <v>1.3209</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2173</v>
+        <v>1.4082</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9473</v>
+        <v>1.1935</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2699</v>
+        <v>0.2147</v>
       </c>
       <c r="V15" t="n">
         <v>0.8865</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. SANCHEZ VIDAL</t>
+          <t>A. PINTO MEDINA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5499</v>
+        <v>1.9422</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3757</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1742</v>
+        <v>1.8731</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5158</v>
+        <v>-1.3549</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6496</v>
+        <v>0.0892</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8663</v>
+        <v>-1.4441</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0565</v>
+        <v>-1.6779</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0565</v>
+        <v>0.2864</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-1.9643</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4593</v>
+        <v>0.323</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4069</v>
+        <v>-0.1972</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8663</v>
+        <v>0.5202</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3774</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5661</v>
+        <v>1.3209</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4115</v>
+        <v>0.1276</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2627</v>
+        <v>0.2192</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1488</v>
+        <v>-0.0916</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>3.7356</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.4148</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ARTIGUES DAÑOBEITIA</t>
+          <t>C. SANCHEZ VIDAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6339</v>
+        <v>1.3503</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6339</v>
+        <v>0.1809</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.1695</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6339</v>
+        <v>1.5158</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6339</v>
+        <v>0.6496</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.8663</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6339</v>
+        <v>1.0565</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6339</v>
+        <v>1.0565</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>0.4593</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.4069</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.8663</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.5661</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.2119</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.0679</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.1441</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Á. PINTO MEDINA</t>
+          <t>J. ARTIGUES DAÑOBEITIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. PINTO MEDINA</t>
+          <t>Á. PINTO MEDINA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5254</v>
+        <v>0.6339</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3206</v>
+        <v>0.6339</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8461</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3549</v>
+        <v>0.6339</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0892</v>
+        <v>0.6339</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4441</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.6779</v>
+        <v>0.6339</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2864</v>
+        <v>0.6339</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.9643</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.323</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1972</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5202</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5661</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3209</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2892</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1706</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1186</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>3.7356</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.4148</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0806</v>
+        <v>0.4931</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5645</v>
+        <v>-0.467</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6451</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6256</v>
@@ -2014,13 +2014,13 @@
         <v>0.9435</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8788</v>
+        <v>-0.4663</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1517</v>
+        <v>-0.0543</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7271</v>
+        <v>-0.4121</v>
       </c>
       <c r="V20" t="n">
         <v>0.6415999999999999</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V. LEMISHKA</t>
+          <t>A. DOMINGUEZ CARRAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0599</v>
+        <v>0.2058</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6447000000000001</v>
+        <v>-0.0345</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5848</v>
+        <v>0.2404</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5949</v>
+        <v>-0.3183</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8007</v>
+        <v>1.4157</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2058</v>
+        <v>-1.734</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0968</v>
+        <v>-0.3275</v>
       </c>
       <c r="K21" t="n">
-        <v>1.8023</v>
+        <v>2.2296</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.899</v>
+        <v>-2.5571</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6917</v>
+        <v>0.0092</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0015</v>
+        <v>-0.8139</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6932</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7548</v>
+        <v>0.5661</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1322</v>
+        <v>1.5096</v>
       </c>
       <c r="S21" t="n">
-        <v>3.175</v>
+        <v>0.2598</v>
       </c>
       <c r="T21" t="n">
-        <v>1.339</v>
+        <v>0.3121</v>
       </c>
       <c r="U21" t="n">
-        <v>1.836</v>
+        <v>-0.0522</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.075</v>
+        <v>-0.3018</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.9244</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.075</v>
+        <v>-1.2262</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1622</v>
+        <v>0.0387</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.237</v>
+        <v>-1.1396</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0749</v>
+        <v>1.1783</v>
       </c>
       <c r="G22" t="n">
         <v>0.1299</v>
@@ -2170,13 +2170,13 @@
         <v>0.5661</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5373</v>
+        <v>-0.3364</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3527</v>
+        <v>-0.2553</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1846</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>0.6226</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ CARRAL</t>
+          <t>H. ENGUIX TORMO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.208</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4243</v>
+        <v>-1.0566</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2163</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3183</v>
+        <v>1.4052</v>
       </c>
       <c r="H23" t="n">
-        <v>1.4157</v>
+        <v>0.3052</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.734</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3275</v>
+        <v>1.8499</v>
       </c>
       <c r="K23" t="n">
-        <v>2.2296</v>
+        <v>0.5337</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.5571</v>
+        <v>1.3162</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0092</v>
+        <v>-0.4447</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8139</v>
+        <v>-0.2285</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8231000000000001</v>
+        <v>-0.2162</v>
       </c>
       <c r="P23" t="n">
+        <v>-2.2644</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-2.8305</v>
+      </c>
+      <c r="R23" t="n">
         <v>0.5661</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-0.9435</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.5096</v>
-      </c>
       <c r="S23" t="n">
-        <v>-0.154</v>
+        <v>0.7688</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.076</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.07630000000000001</v>
+        <v>0.8448</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>H. ENGUIX TORMO</t>
+          <t>F. ALEMANY GARCIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2601</v>
+        <v>-0.3123</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5438</v>
+        <v>-0.0546</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2837</v>
+        <v>-0.2577</v>
       </c>
       <c r="G24" t="n">
-        <v>1.4052</v>
+        <v>0.3744</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3052</v>
+        <v>0.1362</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>0.2383</v>
       </c>
       <c r="J24" t="n">
-        <v>1.8499</v>
+        <v>1.0142</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5337</v>
+        <v>1.0142</v>
       </c>
       <c r="L24" t="n">
-        <v>1.3162</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4447</v>
+        <v>-0.6398</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2285</v>
+        <v>-0.8781</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2162</v>
+        <v>0.2383</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.2644</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.8305</v>
+        <v>-0.9435</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5661</v>
+        <v>0.7548</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5991</v>
+        <v>-0.4981</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5632</v>
+        <v>-0.1254</v>
       </c>
       <c r="U24" t="n">
-        <v>1.1623</v>
+        <v>-0.3727</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>F. ALEMANY GARCIA</t>
+          <t>V. LEMISHKA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4627</v>
+        <v>-1.2373</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1521</v>
+        <v>-1.1319</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3106</v>
+        <v>-0.1054</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3744</v>
+        <v>0.5949</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1362</v>
+        <v>1.8007</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2383</v>
+        <v>-1.2058</v>
       </c>
       <c r="J25" t="n">
-        <v>1.0142</v>
+        <v>-0.0968</v>
       </c>
       <c r="K25" t="n">
-        <v>1.0142</v>
+        <v>1.8023</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>-1.899</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.6398</v>
+        <v>0.6917</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.8781</v>
+        <v>-0.0015</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2383</v>
+        <v>0.6932</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.1887</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R25" t="n">
-        <v>0.7548</v>
+        <v>1.1322</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6484</v>
+        <v>1.9977</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2228</v>
+        <v>0.8519</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4256</v>
+        <v>1.1458</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-3.075</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-3.075</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.0542</v>
+        <v>-2.0849</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.3671</v>
+        <v>-2.9774</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3129</v>
+        <v>0.8925</v>
       </c>
       <c r="G26" t="n">
         <v>-0.9923999999999999</v>
@@ -2482,13 +2482,13 @@
         <v>0.5661</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.0429</v>
+        <v>-0.0735</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6931</v>
+        <v>-0.3034</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3497</v>
+        <v>0.2299</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6415999999999999</v>
@@ -2515,16 +2515,16 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>3.1806</v>
+        <v>3.7279</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.1335</v>
+        <v>-4.6205</v>
       </c>
       <c r="F27" t="n">
-        <v>7.314300000000001</v>
+        <v>8.348699999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5362000000000002</v>
+        <v>0.5362</v>
       </c>
       <c r="H27" t="n">
         <v>3.7172</v>
@@ -2533,16 +2533,16 @@
         <v>-3.181</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.01489999999999991</v>
+        <v>-0.01490000000000014</v>
       </c>
       <c r="K27" t="n">
-        <v>8.213800000000001</v>
+        <v>8.213799999999999</v>
       </c>
       <c r="L27" t="n">
         <v>-8.2286</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5509000000000003</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="N27" t="n">
         <v>-4.4966</v>
@@ -2557,22 +2557,22 @@
         <v>-11.322</v>
       </c>
       <c r="R27" t="n">
-        <v>9.2463</v>
+        <v>9.246300000000002</v>
       </c>
       <c r="S27" t="n">
-        <v>2.8523</v>
+        <v>3.3997</v>
       </c>
       <c r="T27" t="n">
-        <v>2.3172</v>
+        <v>1.8302</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5351000000000005</v>
+        <v>1.5696</v>
       </c>
       <c r="V27" t="n">
-        <v>1.8679</v>
+        <v>1.867899999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>4.885900000000001</v>
+        <v>4.885899999999999</v>
       </c>
       <c r="X27" t="n">
         <v>-3.018</v>
